--- a/files/316_Resistivity_curve_literature.xlsx
+++ b/files/316_Resistivity_curve_literature.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28507"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/peterfelfer/Dropbox/research/01 research Erlangen/05 publications/05:01 papers unfinished to write/2025 wire TDS/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\TDS\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A91BA286-9AA2-A846-85EB-AB0F7511A548}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="820" windowWidth="46980" windowHeight="24000" xr2:uid="{544A7367-F5C4-F14F-9007-7FF33CC866F9}"/>
+    <workbookView xWindow="1560" yWindow="820" windowWidth="46980" windowHeight="24000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -68,7 +67,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1">
     <font>
       <sz val="12"/>
@@ -162,6 +161,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -187,7 +187,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-GB"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -276,40 +276,40 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>28.789360817067291</c:v>
+                  <c:v>20.937716957867121</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>31.901724148642135</c:v>
+                  <c:v>23.201253926285187</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>35.014087480216979</c:v>
+                  <c:v>25.46479089470326</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>37.737405395344958</c:v>
+                  <c:v>27.445385742069064</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>39.68263247757924</c:v>
+                  <c:v>28.860096347330359</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>40.071677894026088</c:v>
+                  <c:v>29.14303846838261</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>40.46072331047295</c:v>
+                  <c:v>29.425980589434872</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>42.016904976260371</c:v>
+                  <c:v>30.557749073643908</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>43.573086642047791</c:v>
+                  <c:v>31.689517557852934</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>44.740222891388363</c:v>
+                  <c:v>32.538343921009712</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>45.518313724282073</c:v>
+                  <c:v>33.104228163114236</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46.685449973622639</c:v>
+                  <c:v>33.953054526271011</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -387,7 +387,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-DE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1210225487"/>
@@ -449,7 +449,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-DE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="366255760"/>
@@ -466,6 +466,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -473,7 +474,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -497,7 +497,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="en-DE"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -1421,16 +1421,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC057F3B-BB78-3643-823A-8CCB2889F6D1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:I14"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.5"/>
   <cols>
     <col min="1" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="26" customWidth="1"/>
-    <col min="5" max="5" width="21.125" customWidth="1"/>
+    <col min="5" max="5" width="21.15234375" customWidth="1"/>
     <col min="6" max="7" width="22" customWidth="1"/>
     <col min="8" max="8" width="19" customWidth="1"/>
-    <col min="9" max="9" width="13.625" customWidth="1"/>
+    <col min="9" max="9" width="13.61328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:9">
@@ -1472,21 +1472,21 @@
       </c>
       <c r="D3">
         <f>C3/1000000 * 10 *$I$3 /$H$7</f>
-        <v>28.789360817067291</v>
+        <v>20.937716957867121</v>
       </c>
       <c r="E3">
         <f>(D4-D3)/(A4-A3) *1000</f>
-        <v>15.561816657874221</v>
+        <v>11.31768484209033</v>
       </c>
       <c r="F3">
         <f>E3/1000 / D3</f>
-        <v>5.4054054054054087E-4</v>
+        <v>5.4054054054054022E-4</v>
       </c>
       <c r="H3">
         <v>60</v>
       </c>
       <c r="I3">
-        <v>110</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -1502,15 +1502,15 @@
       </c>
       <c r="D4">
         <f t="shared" ref="D4:D14" si="1">C4/1000000 * 10 *$I$3 /$H$7</f>
-        <v>31.901724148642135</v>
+        <v>23.201253926285187</v>
       </c>
       <c r="E4">
         <f t="shared" ref="E4:E13" si="2">(D5-D4)/(A5-A4) *1000</f>
-        <v>15.561816657874221</v>
+        <v>11.317684842090365</v>
       </c>
       <c r="F4">
         <f t="shared" ref="F4:F13" si="3">E4/1000 / D4</f>
-        <v>4.8780487804878076E-4</v>
+        <v>4.8780487804878184E-4</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1526,15 +1526,15 @@
       </c>
       <c r="D5">
         <f t="shared" si="1"/>
-        <v>35.014087480216979</v>
+        <v>25.46479089470326</v>
       </c>
       <c r="E5">
         <f t="shared" si="2"/>
-        <v>13.616589575639892</v>
+        <v>9.9029742368290208</v>
       </c>
       <c r="F5">
         <f t="shared" si="3"/>
-        <v>3.8888888888888762E-4</v>
+        <v>3.8888888888888789E-4</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1550,15 +1550,15 @@
       </c>
       <c r="D6">
         <f t="shared" si="1"/>
-        <v>37.737405395344958</v>
+        <v>27.445385742069064</v>
       </c>
       <c r="E6">
         <f t="shared" si="2"/>
-        <v>12.968180548228551</v>
+        <v>9.4314040350752979</v>
       </c>
       <c r="F6">
         <f t="shared" si="3"/>
-        <v>3.4364261168384991E-4</v>
+        <v>3.4364261168384947E-4</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -1577,15 +1577,15 @@
       </c>
       <c r="D7">
         <f t="shared" si="1"/>
-        <v>39.68263247757924</v>
+        <v>28.860096347330359</v>
       </c>
       <c r="E7">
         <f t="shared" si="2"/>
-        <v>7.7809083289369596</v>
+        <v>5.6588424210450228</v>
       </c>
       <c r="F7">
         <f t="shared" si="3"/>
-        <v>1.9607843137254533E-4</v>
+        <v>1.9607843137254397E-4</v>
       </c>
       <c r="H7">
         <f>(H3/1000)^2 * PI() /4</f>
@@ -1605,15 +1605,15 @@
       </c>
       <c r="D8">
         <f t="shared" si="1"/>
-        <v>40.071677894026088</v>
+        <v>29.14303846838261</v>
       </c>
       <c r="E8">
         <f t="shared" si="2"/>
-        <v>7.7809083289372438</v>
+        <v>5.6588424210452359</v>
       </c>
       <c r="F8">
         <f t="shared" si="3"/>
-        <v>1.9417475728155688E-4</v>
+        <v>1.9417475728155577E-4</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -1629,15 +1629,15 @@
       </c>
       <c r="D9">
         <f t="shared" si="1"/>
-        <v>40.46072331047295</v>
+        <v>29.425980589434872</v>
       </c>
       <c r="E9">
         <f t="shared" si="2"/>
-        <v>10.374544438582802</v>
+        <v>7.5451232280602429</v>
       </c>
       <c r="F9">
         <f t="shared" si="3"/>
-        <v>2.5641025641025625E-4</v>
+        <v>2.5641025641025706E-4</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -1653,15 +1653,15 @@
       </c>
       <c r="D10">
         <f t="shared" si="1"/>
-        <v>42.016904976260371</v>
+        <v>30.557749073643908</v>
       </c>
       <c r="E10">
         <f t="shared" si="2"/>
-        <v>7.7809083289371017</v>
+        <v>5.6588424210451294</v>
       </c>
       <c r="F10">
         <f t="shared" si="3"/>
-        <v>1.8518518518518509E-4</v>
+        <v>1.851851851851839E-4</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -1677,15 +1677,15 @@
       </c>
       <c r="D11">
         <f t="shared" si="1"/>
-        <v>43.573086642047791</v>
+        <v>31.689517557852934</v>
       </c>
       <c r="E11">
         <f t="shared" si="2"/>
-        <v>5.8356812467028618</v>
+        <v>4.2441318157838914</v>
       </c>
       <c r="F11">
         <f t="shared" si="3"/>
-        <v>1.3392857142857217E-4</v>
+        <v>1.3392857142857195E-4</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -1701,15 +1701,15 @@
       </c>
       <c r="D12">
         <f t="shared" si="1"/>
-        <v>44.740222891388363</v>
+        <v>32.538343921009712</v>
       </c>
       <c r="E12">
         <f t="shared" si="2"/>
-        <v>3.8904541644685509</v>
+        <v>2.829421210522618</v>
       </c>
       <c r="F12">
         <f t="shared" si="3"/>
-        <v>8.6956521739130387E-5</v>
+        <v>8.6956521739131484E-5</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -1725,11 +1725,11 @@
       </c>
       <c r="D13">
         <f t="shared" si="1"/>
-        <v>45.518313724282073</v>
+        <v>33.104228163114236</v>
       </c>
       <c r="E13">
         <f t="shared" si="2"/>
-        <v>5.8356812467028263</v>
+        <v>4.2441318157838737</v>
       </c>
       <c r="F13">
         <f t="shared" si="3"/>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="D14">
         <f t="shared" si="1"/>
-        <v>46.685449973622639</v>
+        <v>33.953054526271011</v>
       </c>
     </row>
   </sheetData>

--- a/files/316_Resistivity_curve_literature.xlsx
+++ b/files/316_Resistivity_curve_literature.xlsx
@@ -279,43 +279,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>117.77465788800255</c:v>
+                  <c:v>37.687890524160814</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>124.14085561167836</c:v>
+                  <c:v>39.725073795737075</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>130.50705333535419</c:v>
+                  <c:v>41.762257067313335</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>143.23944878270584</c:v>
+                  <c:v>45.836623610465857</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>154.38029479913845</c:v>
+                  <c:v>49.401694335724301</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>162.33804195373327</c:v>
+                  <c:v>51.948173425194639</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>163.92959138465218</c:v>
+                  <c:v>52.457469243088696</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>165.52114081557116</c:v>
+                  <c:v>52.966765060982766</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>171.88733853924697</c:v>
+                  <c:v>55.003948332559027</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>178.25353626292278</c:v>
+                  <c:v>57.04113160413528</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>183.02818455567964</c:v>
+                  <c:v>58.569019057817478</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>186.21128341751756</c:v>
+                  <c:v>59.587610693605612</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>190.98593171027443</c:v>
+                  <c:v>61.115498147287809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1478,21 +1478,21 @@
       </c>
       <c r="D3">
         <f t="shared" ref="D3:D15" si="0">C3/1000000 * 10 *$I$3 /$H$8</f>
-        <v>117.77465788800255</v>
+        <v>37.687890524160814</v>
       </c>
       <c r="E3">
         <f>(D5-D3)/(A5-A3) *1000</f>
-        <v>63.661977236758176</v>
+        <v>20.371832715762608</v>
       </c>
       <c r="F3">
         <f>E3/1000 / D3</f>
-        <v>5.4054054054054087E-4</v>
+        <v>5.4054054054054066E-4</v>
       </c>
       <c r="H3">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I3">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -1508,15 +1508,15 @@
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>124.14085561167836</v>
+        <v>39.725073795737075</v>
       </c>
       <c r="E4">
         <f>(D6-D4)/(A6-A4) *1000</f>
-        <v>59.128771427329639</v>
+        <v>18.921206856745457</v>
       </c>
       <c r="F4">
         <f>E4/1000 / D4</f>
-        <v>4.7630388187663814E-4</v>
+        <v>4.7630388187663739E-4</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1532,15 +1532,15 @@
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>130.50705333535419</v>
+        <v>41.762257067313335</v>
       </c>
       <c r="E5">
         <f t="shared" ref="E5:E14" si="2">(D6-D5)/(A6-A5) *1000</f>
-        <v>63.661977236758247</v>
+        <v>20.371832715762608</v>
       </c>
       <c r="F5">
         <f t="shared" ref="F5:F14" si="3">E5/1000 / D5</f>
-        <v>4.878048780487813E-4</v>
+        <v>4.8780487804878065E-4</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1556,15 +1556,15 @@
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>143.23944878270584</v>
+        <v>45.836623610465857</v>
       </c>
       <c r="E6">
         <f t="shared" si="2"/>
-        <v>55.704230082163093</v>
+        <v>17.82535362629222</v>
       </c>
       <c r="F6">
         <f t="shared" si="3"/>
-        <v>3.8888888888888692E-4</v>
+        <v>3.8888888888888757E-4</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -1580,15 +1580,15 @@
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
-        <v>154.38029479913845</v>
+        <v>49.401694335724301</v>
       </c>
       <c r="E7">
         <f t="shared" si="2"/>
-        <v>53.051647697298755</v>
+        <v>16.976527263135587</v>
       </c>
       <c r="F7">
         <f t="shared" si="3"/>
-        <v>3.4364261168385083E-4</v>
+        <v>3.4364261168385061E-4</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -1607,19 +1607,19 @@
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
-        <v>162.33804195373327</v>
+        <v>51.948173425194639</v>
       </c>
       <c r="E8">
         <f t="shared" si="2"/>
-        <v>31.830988618378338</v>
+        <v>10.185916357881126</v>
       </c>
       <c r="F8">
         <f t="shared" si="3"/>
-        <v>1.9607843137254451E-4</v>
+        <v>1.9607843137254562E-4</v>
       </c>
       <c r="H8">
         <f>(H3/1000)^2 * PI() /4</f>
-        <v>1.2566370614359172E-3</v>
+        <v>1.9634954084936209E-3</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -1635,15 +1635,15 @@
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
-        <v>163.92959138465218</v>
+        <v>52.457469243088696</v>
       </c>
       <c r="E9">
         <f t="shared" si="2"/>
-        <v>31.830988618379479</v>
+        <v>10.18591635788141</v>
       </c>
       <c r="F9">
         <f t="shared" si="3"/>
-        <v>1.9417475728155591E-4</v>
+        <v>1.941747572815555E-4</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -1659,15 +1659,15 @@
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
-        <v>165.52114081557116</v>
+        <v>52.966765060982766</v>
       </c>
       <c r="E10">
         <f t="shared" si="2"/>
-        <v>42.441318157838737</v>
+        <v>13.581221810508405</v>
       </c>
       <c r="F10">
         <f t="shared" si="3"/>
-        <v>2.5641025641025625E-4</v>
+        <v>2.5641025641025646E-4</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -1683,15 +1683,15 @@
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
-        <v>171.88733853924697</v>
+        <v>55.003948332559027</v>
       </c>
       <c r="E11">
         <f t="shared" si="2"/>
-        <v>31.830988618379052</v>
+        <v>10.185916357881268</v>
       </c>
       <c r="F11">
         <f t="shared" si="3"/>
-        <v>1.8518518518518509E-4</v>
+        <v>1.8518518518518458E-4</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -1707,15 +1707,15 @@
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
-        <v>178.25353626292278</v>
+        <v>57.04113160413528</v>
       </c>
       <c r="E12">
         <f t="shared" si="2"/>
-        <v>23.873241463784325</v>
+        <v>7.6394372684109868</v>
       </c>
       <c r="F12">
         <f t="shared" si="3"/>
-        <v>1.3392857142857154E-4</v>
+        <v>1.3392857142857162E-4</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -1731,15 +1731,15 @@
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
-        <v>183.02818455567964</v>
+        <v>58.569019057817478</v>
       </c>
       <c r="E13">
         <f t="shared" si="2"/>
-        <v>15.915494309189596</v>
+        <v>5.0929581789406697</v>
       </c>
       <c r="F13">
         <f t="shared" si="3"/>
-        <v>8.695652173913078E-5</v>
+        <v>8.6956521739130766E-5</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -1755,15 +1755,15 @@
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
-        <v>186.21128341751756</v>
+        <v>59.587610693605612</v>
       </c>
       <c r="E14">
         <f t="shared" si="2"/>
-        <v>23.873241463784325</v>
+        <v>7.6394372684109868</v>
       </c>
       <c r="F14">
         <f t="shared" si="3"/>
-        <v>1.2820512820512831E-4</v>
+        <v>1.2820512820512839E-4</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="D15">
         <f t="shared" si="0"/>
-        <v>190.98593171027443</v>
+        <v>61.115498147287809</v>
       </c>
     </row>
   </sheetData>
